--- a/test_export_2026-10-19.xlsx
+++ b/test_export_2026-10-19.xlsx
@@ -604,7 +604,7 @@
         <v>Export Date</v>
       </c>
       <c r="B3" t="str">
-        <v>10/19/2026, 3:53:18 AM</v>
+        <v>10/19/2026, 8:28:28 AM</v>
       </c>
     </row>
     <row r="4">

--- a/test_export_2026-10-19.xlsx
+++ b/test_export_2026-10-19.xlsx
@@ -604,7 +604,7 @@
         <v>Export Date</v>
       </c>
       <c r="B3" t="str">
-        <v>10/19/2026, 8:28:28 AM</v>
+        <v>10/19/2026, 1:51:34 PM</v>
       </c>
     </row>
     <row r="4">
